--- a/forms/trg/Formulir_TRG_marine-natural.xlsx
+++ b/forms/trg/Formulir_TRG_marine-natural.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nur Asmi</t>
+          <t>Prof. Dr. Nunuk Hariani Soekamto, M.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -931,15 +931,11 @@
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6366-1832</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57214768639</t>
+          <t>7801574264</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Riska Mardiyanti, M.Sc</t>
+          <t>Dr. Nur Asmi</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -974,11 +970,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-6052-6938</t>
+          <t>0000-0001-6366-1832</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57214768639</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -991,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Drs. Fredryk Mandey, M.Sc.</t>
+          <t>Riska Mardiyanti, M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1011,15 +1011,11 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8502-0227</t>
+          <t>0009-0006-6052-6938</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>55791657200</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Herlina Rasyid</t>
+          <t>Drs. Fredryk Mandey, M.Sc.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1052,13 +1048,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9136-9716</t>
+          <t>0000-0001-8502-0227</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57204505767</t>
+          <t>55791657200</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1073,12 +1069,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ajuk Sapar, M.Si</t>
+          <t>Dr. Herlina Rasyid</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1093,13 +1089,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7278-6159</t>
+          <t>0000-0001-9136-9716</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57210808617</t>
+          <t>57204505767</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1114,17 +1110,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Tatsufumi Okino</t>
+          <t>Dr. Ajuk Sapar, M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hokkaido University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1132,11 +1128,15 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7278-6159</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>7005917192</t>
+          <t>57210808617</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1151,27 +1151,31 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Bahrun, M.Si</t>
+          <t>Prof. Dr. Tatsufumi Okino</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>BRIN</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Hokkaido University</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>7005917192</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1184,35 +1188,27 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ajuk Sapar, M.Si</t>
+          <t>Dr. Bahrun, M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>BRIN</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7278-6159</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>57210808617</t>
-        </is>
-      </c>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1225,12 +1221,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Herlina Rasyid</t>
+          <t>Dr. Ajuk Sapar, M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1245,13 +1241,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9136-9716</t>
+          <t>0000-0002-7278-6159</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57204505767</t>
+          <t>57210808617</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1266,12 +1262,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Drs. Fredryk Mandey, M.Sc</t>
+          <t>Dr. Herlina Rasyid</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1284,9 +1280,17 @@
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9136-9716</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57204505767</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1299,12 +1303,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Riska Mardiyanti, M.Sc</t>
+          <t>Drs. Fredryk Mandey, M.Sc</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1317,11 +1321,7 @@
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0009-0006-6052-6938</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nur Asmi</t>
+          <t>Riska Mardiyanti, M.Sc</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1356,15 +1356,11 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6366-1832</t>
+          <t>0009-0006-6052-6938</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>57214768639</t>
-        </is>
-      </c>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1377,33 +1373,33 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Dr. Bahrun, M.Si</t>
+          <t>Dr. Nur Asmi</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN)</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5243-014X</t>
+          <t>0000-0001-6366-1832</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>57222651409</t>
+          <t>57214768639</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1418,29 +1414,33 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Al Mustawa, S.Si., M.Si.</t>
+          <t>Dr. Bahrun, M.Si</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN)</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5243-014X</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>58029347800</t>
+          <t>57222651409</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Andi Akbar</t>
+          <t>Muhammad Al Mustawa, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1475,7 +1475,11 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>58029347800</t>
+        </is>
+      </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1488,12 +1492,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dewi Wulandari</t>
+          <t>Andi Akbar</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1521,12 +1525,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Sepriani Kombong Kila’</t>
+          <t>Dewi Wulandari</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1554,12 +1558,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Syahdam Karneng</t>
+          <t>Sepriani Kombong Kila’</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1587,12 +1591,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Taufiq Dalming</t>
+          <t>Syahdam Karneng</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1600,11 +1604,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>MANAPROCHEM Team</t>
-        </is>
-      </c>
+      <c r="E23" s="11" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -1622,10 +1622,26 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Taufiq Dalming</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>MANAPROCHEM Team</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1633,7 +1649,11 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1822,15 +1842,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
